--- a/past/2023/02-23-sny.xlsx
+++ b/past/2023/02-23-sny.xlsx
@@ -5,29 +5,30 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\aaGitMe\past\2023\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\aaGitMe_2026\26-yzhn\past\2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0C0189E-00E5-4F7A-A37F-D9456B45B6EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2192081-31D0-4868-89B1-B7761FBC6AEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="912" firstSheet="1" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="912" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="TPLM" sheetId="1" r:id="rId1"/>
-    <sheet name="SnyA105-22" sheetId="2" r:id="rId2"/>
-    <sheet name="SnyB202-22" sheetId="3" r:id="rId3"/>
-    <sheet name="SnyC301-22" sheetId="4" r:id="rId4"/>
-    <sheet name="SnyE502-22" sheetId="5" r:id="rId5"/>
-    <sheet name="SnyF601-22" sheetId="6" r:id="rId6"/>
-    <sheet name="Sayfa1" sheetId="15" r:id="rId7"/>
-    <sheet name="SnyG702-22" sheetId="7" r:id="rId8"/>
-    <sheet name="SnH_yazıhane" sheetId="8" r:id="rId9"/>
-    <sheet name="02-10-TPLM" sheetId="9" r:id="rId10"/>
-    <sheet name="02-11-GLR" sheetId="10" r:id="rId11"/>
-    <sheet name="02-12-GDR" sheetId="11" r:id="rId12"/>
-    <sheet name="02-13-BKY" sheetId="12" r:id="rId13"/>
-    <sheet name="02-14-BKY" sheetId="13" r:id="rId14"/>
-    <sheet name="02-13-BAKIYE" sheetId="14" r:id="rId15"/>
+    <sheet name="Sayfa2" sheetId="16" r:id="rId1"/>
+    <sheet name="TPLM" sheetId="1" r:id="rId2"/>
+    <sheet name="SnyA105-22" sheetId="2" r:id="rId3"/>
+    <sheet name="SnyB202-22" sheetId="3" r:id="rId4"/>
+    <sheet name="SnyC301-22" sheetId="4" r:id="rId5"/>
+    <sheet name="SnyE502-22" sheetId="5" r:id="rId6"/>
+    <sheet name="SnyF601-22" sheetId="6" r:id="rId7"/>
+    <sheet name="Sayfa1" sheetId="15" r:id="rId8"/>
+    <sheet name="SnyG702-22" sheetId="7" r:id="rId9"/>
+    <sheet name="SnH_yazıhane" sheetId="8" r:id="rId10"/>
+    <sheet name="02-10-TPLM" sheetId="9" r:id="rId11"/>
+    <sheet name="02-11-GLR" sheetId="10" r:id="rId12"/>
+    <sheet name="02-12-GDR" sheetId="11" r:id="rId13"/>
+    <sheet name="02-13-BKY" sheetId="12" r:id="rId14"/>
+    <sheet name="02-14-BKY" sheetId="13" r:id="rId15"/>
+    <sheet name="02-13-BAKIYE" sheetId="14" r:id="rId16"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1236" uniqueCount="620">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1246" uniqueCount="627">
   <si>
     <t>2022-23</t>
   </si>
@@ -2236,6 +2237,27 @@
   </si>
   <si>
     <t>31-3-2022 Asgari ücret 4253 TL</t>
+  </si>
+  <si>
+    <t>toplam</t>
+  </si>
+  <si>
+    <t>kesinti</t>
+  </si>
+  <si>
+    <t>kesintili</t>
+  </si>
+  <si>
+    <t>kesintisiz</t>
+  </si>
+  <si>
+    <t>yıkamacı</t>
+  </si>
+  <si>
+    <t>hurdacı</t>
+  </si>
+  <si>
+    <t>ykmc</t>
   </si>
 </sst>
 </file>
@@ -3880,6 +3902,15 @@
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="170" fontId="34" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="34" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="174" fontId="34" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3894,17 +3925,44 @@
     <xf numFmtId="174" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="34" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="34" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="34" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="34" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="34" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="34" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="40" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="174" fontId="34" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="40" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="40" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="40" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="34" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3916,42 +3974,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="40" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="40" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="34" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="40" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="174" fontId="34" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="40" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="174" fontId="34" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="34" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4286,237 +4308,538 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A6:F22"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4369006-062D-451F-A2FD-3EDEBA202C1A}">
+  <dimension ref="C4:G22"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetData>
+    <row r="4" spans="3:7">
+      <c r="D4" t="s">
+        <v>620</v>
+      </c>
+      <c r="E4" t="s">
+        <v>621</v>
+      </c>
+      <c r="F4" t="s">
+        <v>622</v>
+      </c>
+      <c r="G4" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="5" spans="3:7">
+      <c r="D5">
+        <v>259550</v>
+      </c>
+      <c r="E5">
+        <v>41955</v>
+      </c>
+      <c r="F5">
+        <f>E5/20*100</f>
+        <v>209775</v>
+      </c>
+      <c r="G5">
+        <f>D5-F5</f>
+        <v>49775</v>
+      </c>
+    </row>
+    <row r="7" spans="3:7">
+      <c r="F7" t="s">
+        <v>624</v>
+      </c>
+      <c r="G7">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="10" spans="3:7">
+      <c r="C10" t="s">
+        <v>625</v>
+      </c>
+      <c r="D10">
+        <v>135000</v>
+      </c>
+    </row>
+    <row r="11" spans="3:7">
+      <c r="C11" t="s">
+        <v>500</v>
+      </c>
+      <c r="D11">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="12" spans="3:7">
+      <c r="C12" t="s">
+        <v>502</v>
+      </c>
+      <c r="D12">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="13" spans="3:7">
+      <c r="C13" t="s">
+        <v>626</v>
+      </c>
+      <c r="D13">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="14" spans="3:7">
+      <c r="C14" t="s">
+        <v>499</v>
+      </c>
+      <c r="D14">
+        <v>28080</v>
+      </c>
+    </row>
+    <row r="15" spans="3:7">
+      <c r="D15">
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="16" spans="3:7">
+      <c r="D16">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="17" spans="4:4">
+      <c r="D17">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="18" spans="4:4">
+      <c r="D18">
+        <v>2120</v>
+      </c>
+    </row>
+    <row r="19" spans="4:4">
+      <c r="D19">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="22" spans="4:4">
+      <c r="D22">
+        <f>SUM(D10:D19)</f>
+        <v>213800</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:G48"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="12.140625" customWidth="1"/>
-    <col min="2" max="2" width="26.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" customWidth="1"/>
-    <col min="6" max="6" width="10.5703125" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
+    <col min="2" max="2" width="23.7109375" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="9.42578125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="11.28515625" style="3" customWidth="1"/>
+    <col min="8" max="59" width="12.140625" customWidth="1"/>
+    <col min="60" max="60" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="6" spans="1:6">
-      <c r="A6" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="C7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="2" t="s">
+    <row r="1" spans="1:7">
+      <c r="B1" s="1"/>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>2023</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F2" s="57">
+        <f>SUM(F6:F56)</f>
+        <v>5725.95</v>
+      </c>
+      <c r="G2" s="57">
+        <f>F2</f>
+        <v>5725.95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="99" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="99" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="100" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" t="s">
-        <v>7</v>
+      <c r="E4" s="100" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="100" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" s="100" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="F5" s="97"/>
+      <c r="G5" s="57"/>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="60">
+        <v>44956</v>
+      </c>
+      <c r="B6" t="s">
+        <v>255</v>
+      </c>
+      <c r="C6"/>
+      <c r="D6"/>
+      <c r="F6" s="3">
+        <v>87.69</v>
+      </c>
+      <c r="G6" s="3">
+        <f t="shared" ref="G6:G23" si="0">G5+E6-F6</f>
+        <v>-87.69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="60">
+        <v>44985</v>
+      </c>
+      <c r="B7" t="s">
+        <v>256</v>
+      </c>
+      <c r="C7"/>
+      <c r="D7"/>
+      <c r="F7" s="3">
+        <v>54.93</v>
+      </c>
+      <c r="G7" s="3">
+        <f t="shared" si="0"/>
+        <v>-142.62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="60">
+        <v>45015</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="3">
-        <f>'SnyA105-22'!E4</f>
-        <v>84000</v>
-      </c>
-      <c r="D8" s="3">
-        <f>'SnyA105-22'!F4</f>
-        <v>84000</v>
-      </c>
-      <c r="E8" s="4">
-        <f t="shared" ref="E8:E13" si="0">C8-D8</f>
-        <v>0</v>
-      </c>
-      <c r="F8" s="4">
-        <f>'SnyA105-22'!E6</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" t="s">
-        <v>9</v>
+        <v>257</v>
+      </c>
+      <c r="C8"/>
+      <c r="D8"/>
+      <c r="F8" s="3">
+        <v>97.14</v>
+      </c>
+      <c r="G8" s="3">
+        <f t="shared" si="0"/>
+        <v>-239.76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="60">
+        <v>45046</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="3">
-        <f>'SnyB202-22'!D4</f>
-        <v>0</v>
-      </c>
-      <c r="D9" s="3">
-        <f>'SnyB202-22'!E4</f>
-        <v>0</v>
-      </c>
-      <c r="E9" s="4">
+        <v>258</v>
+      </c>
+      <c r="C9"/>
+      <c r="D9"/>
+      <c r="F9" s="3">
+        <v>99.31</v>
+      </c>
+      <c r="G9" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F9" s="4">
-        <f>'SnyB202-22'!D6</f>
-        <v>-1000.1199999999998</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" t="s">
-        <v>11</v>
+        <v>-339.07</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="60">
+        <v>45076</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="3">
-        <f>'SnyC301-22'!D4</f>
-        <v>240000</v>
-      </c>
-      <c r="D10" s="3">
-        <f>'SnyC301-22'!E4</f>
-        <v>135000</v>
-      </c>
-      <c r="E10" s="4">
+        <v>259</v>
+      </c>
+      <c r="C10"/>
+      <c r="D10"/>
+      <c r="F10" s="3">
+        <v>34.06</v>
+      </c>
+      <c r="G10" s="3">
         <f t="shared" si="0"/>
-        <v>105000</v>
-      </c>
-      <c r="F10" s="4">
-        <f>'SnyC301-22'!D6</f>
-        <v>-3924.1099999999997</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="3">
-        <f>'SnyE502-22'!D4</f>
-        <v>96000</v>
-      </c>
-      <c r="D11" s="3">
-        <f>'SnyE502-22'!E4</f>
-        <v>89000</v>
-      </c>
-      <c r="E11" s="4">
+        <v>-373.13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="101">
+        <v>45060</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C11"/>
+      <c r="D11"/>
+      <c r="F11" s="3">
+        <v>1095</v>
+      </c>
+      <c r="G11" s="3">
         <f t="shared" si="0"/>
-        <v>7000</v>
-      </c>
-      <c r="F11" s="4">
-        <f>'SnyE502-22'!D6</f>
-        <v>-800</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="3">
-        <f>'SnyF601-22'!D4</f>
-        <v>109312.51909485454</v>
-      </c>
-      <c r="D12" s="3">
-        <f>'SnyF601-22'!E4</f>
-        <v>109312.51999999999</v>
-      </c>
-      <c r="E12" s="4">
+        <v>-1468.13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="101">
+        <v>45060</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="C12"/>
+      <c r="D12"/>
+      <c r="F12" s="3">
+        <v>109.5</v>
+      </c>
+      <c r="G12" s="3">
         <f t="shared" si="0"/>
-        <v>-9.0514545445330441E-4</v>
-      </c>
-      <c r="F12" s="4">
-        <f>'SnyF601-22'!D6</f>
-        <v>-2510.63</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" t="s">
-        <v>17</v>
+        <v>-1577.63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="60">
+        <v>45107</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="3">
-        <f>'SnyG702-22'!D4</f>
-        <v>96000</v>
-      </c>
-      <c r="D13" s="3">
-        <f>'SnyG702-22'!E4</f>
-        <v>96000</v>
-      </c>
-      <c r="E13" s="4">
+        <v>262</v>
+      </c>
+      <c r="C13"/>
+      <c r="D13"/>
+      <c r="F13" s="3">
+        <v>22.7</v>
+      </c>
+      <c r="G13" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F13" s="4">
-        <f>'SnyG702-22'!D6</f>
-        <v>-1200</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" t="s">
-        <v>19</v>
+        <v>-1600.3300000000002</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="60">
+        <v>45137</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="4">
-        <f>SnH_yazıhane!F2*-1</f>
+        <v>263</v>
+      </c>
+      <c r="C14"/>
+      <c r="D14"/>
+      <c r="F14" s="3">
+        <v>31.73</v>
+      </c>
+      <c r="G14" s="3">
+        <f t="shared" si="0"/>
+        <v>-1632.0600000000002</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="60">
+        <v>45168</v>
+      </c>
+      <c r="B15" t="s">
+        <v>264</v>
+      </c>
+      <c r="C15"/>
+      <c r="D15"/>
+      <c r="F15" s="3">
+        <v>34.99</v>
+      </c>
+      <c r="G15" s="3">
+        <f t="shared" si="0"/>
+        <v>-1667.0500000000002</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="60">
+        <v>45199</v>
+      </c>
+      <c r="B16" t="s">
+        <v>265</v>
+      </c>
+      <c r="C16"/>
+      <c r="D16"/>
+      <c r="F16" s="3">
+        <v>23.73</v>
+      </c>
+      <c r="G16" s="3">
+        <f t="shared" si="0"/>
+        <v>-1690.7800000000002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="60">
+        <v>45229</v>
+      </c>
+      <c r="B17" t="s">
+        <v>266</v>
+      </c>
+      <c r="C17"/>
+      <c r="D17"/>
+      <c r="F17" s="3">
+        <v>41.12</v>
+      </c>
+      <c r="G17" s="3">
+        <f t="shared" si="0"/>
+        <v>-1731.9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="101">
+        <v>45213</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C18"/>
+      <c r="D18"/>
+      <c r="F18" s="3">
+        <v>1095</v>
+      </c>
+      <c r="G18" s="3">
+        <f t="shared" si="0"/>
+        <v>-2826.9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="101">
+        <v>45213</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C19"/>
+      <c r="D19"/>
+      <c r="F19" s="3">
+        <v>109.5</v>
+      </c>
+      <c r="G19" s="3">
+        <f t="shared" si="0"/>
+        <v>-2936.4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="361">
+        <v>45257</v>
+      </c>
+      <c r="B20" t="s">
+        <v>600</v>
+      </c>
+      <c r="F20" s="3">
+        <v>2500</v>
+      </c>
+      <c r="G20" s="3">
+        <f t="shared" si="0"/>
+        <v>-5436.4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="60">
+        <v>45260</v>
+      </c>
+      <c r="B21" t="s">
+        <v>267</v>
+      </c>
+      <c r="C21"/>
+      <c r="D21"/>
+      <c r="F21" s="3">
+        <v>41.54</v>
+      </c>
+      <c r="G21" s="3">
+        <f t="shared" si="0"/>
+        <v>-5477.94</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="60">
+        <v>45290</v>
+      </c>
+      <c r="B22" t="s">
+        <v>270</v>
+      </c>
+      <c r="C22"/>
+      <c r="F22" s="3">
+        <v>128.01</v>
+      </c>
+      <c r="G22" s="3">
+        <f t="shared" si="0"/>
+        <v>-5605.95</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="B23" t="s">
+        <v>144</v>
+      </c>
+      <c r="C23"/>
+      <c r="D23"/>
+      <c r="E23"/>
+      <c r="F23">
+        <v>120</v>
+      </c>
+      <c r="G23" s="3">
+        <f t="shared" si="0"/>
         <v>-5725.95</v>
       </c>
-      <c r="D14" s="4">
-        <f>C14</f>
-        <v>-5725.95</v>
-      </c>
-      <c r="E14" s="4">
-        <f>C14-D14</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="E15" s="4"/>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="B16" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="6">
-        <f>SUM(C8:C14)</f>
-        <v>619586.56909485464</v>
-      </c>
-      <c r="D16" s="6">
-        <f>SUM(D8:D14)</f>
-        <v>507586.57</v>
-      </c>
-      <c r="E16" s="6">
-        <f>SUM(E8:E14)</f>
-        <v>111999.99909485455</v>
-      </c>
-      <c r="F16" s="6">
-        <f>SUM(F8:F14)</f>
-        <v>-9434.86</v>
-      </c>
-    </row>
-    <row r="18" spans="4:4">
-      <c r="D18" s="359"/>
-    </row>
-    <row r="22" spans="4:4">
-      <c r="D22" s="361"/>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="C24"/>
+      <c r="D24"/>
+      <c r="E24"/>
+      <c r="F24"/>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="D25"/>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="60"/>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="60"/>
+      <c r="B27" s="3"/>
+      <c r="D27"/>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="60"/>
+      <c r="B28" s="3"/>
+      <c r="D28"/>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="E32" s="1"/>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="E33" s="1"/>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="E34" s="1"/>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="60"/>
+      <c r="E35" s="1"/>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="60"/>
+      <c r="E36" s="1"/>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="E37" s="1"/>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="60"/>
+      <c r="E38" s="1"/>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="G48" s="57"/>
     </row>
   </sheetData>
   <pageMargins left="0.39370078740157505" right="0.23622047244094502" top="0.70905511811023614" bottom="0.7062992125984251" header="0.31535433070866109" footer="0.3125984251968501"/>
@@ -4525,7 +4848,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:L21"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
@@ -4816,7 +5139,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="B1:M108"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
@@ -6758,7 +7081,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:AMJ1048574"/>
   <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="11.25" customHeight="1"/>
@@ -9148,7 +9471,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:AMJ1048548"/>
   <sheetFormatPr defaultRowHeight="11.25" customHeight="1"/>
@@ -9195,21 +9518,21 @@
       <c r="D2" s="156"/>
       <c r="E2" s="157"/>
       <c r="F2" s="156"/>
-      <c r="G2" s="367" t="s">
+      <c r="G2" s="362" t="s">
         <v>468</v>
       </c>
-      <c r="H2" s="367"/>
-      <c r="I2" s="367"/>
-      <c r="J2" s="367"/>
-      <c r="K2" s="367"/>
+      <c r="H2" s="362"/>
+      <c r="I2" s="362"/>
+      <c r="J2" s="362"/>
+      <c r="K2" s="362"/>
       <c r="L2" s="156"/>
-      <c r="M2" s="367" t="s">
+      <c r="M2" s="362" t="s">
         <v>469</v>
       </c>
-      <c r="N2" s="367"/>
-      <c r="O2" s="367"/>
-      <c r="P2" s="367"/>
-      <c r="Q2" s="367"/>
+      <c r="N2" s="362"/>
+      <c r="O2" s="362"/>
+      <c r="P2" s="362"/>
+      <c r="Q2" s="362"/>
       <c r="R2" s="156"/>
       <c r="S2" s="158"/>
     </row>
@@ -9221,23 +9544,23 @@
       <c r="E3" s="160" t="s">
         <v>471</v>
       </c>
-      <c r="G3" s="368" t="s">
+      <c r="G3" s="363" t="s">
         <v>472</v>
       </c>
-      <c r="H3" s="368"/>
-      <c r="J3" s="369" t="s">
+      <c r="H3" s="363"/>
+      <c r="J3" s="364" t="s">
         <v>473</v>
       </c>
-      <c r="K3" s="369"/>
-      <c r="M3" s="368" t="s">
+      <c r="K3" s="364"/>
+      <c r="M3" s="363" t="s">
         <v>472</v>
       </c>
-      <c r="N3" s="368"/>
-      <c r="O3" s="368"/>
-      <c r="P3" s="369" t="s">
+      <c r="N3" s="363"/>
+      <c r="O3" s="363"/>
+      <c r="P3" s="364" t="s">
         <v>473</v>
       </c>
-      <c r="Q3" s="369"/>
+      <c r="Q3" s="364"/>
       <c r="S3" s="161" t="s">
         <v>353</v>
       </c>
@@ -9300,11 +9623,11 @@
         <v>450000</v>
       </c>
       <c r="F5" s="157"/>
-      <c r="G5" s="362">
+      <c r="G5" s="365">
         <f>K5/$E$5</f>
         <v>0.5</v>
       </c>
-      <c r="H5" s="362"/>
+      <c r="H5" s="365"/>
       <c r="I5" s="176"/>
       <c r="J5" s="177" t="s">
         <v>477</v>
@@ -9313,11 +9636,11 @@
         <v>225000</v>
       </c>
       <c r="L5" s="178"/>
-      <c r="M5" s="363">
+      <c r="M5" s="366">
         <f>Q5/$E$5</f>
         <v>0.5</v>
       </c>
-      <c r="N5" s="363"/>
+      <c r="N5" s="366"/>
       <c r="O5" s="179"/>
       <c r="P5" s="176"/>
       <c r="Q5" s="175">
@@ -9337,11 +9660,11 @@
         <v>478</v>
       </c>
       <c r="F6" s="165"/>
-      <c r="G6" s="364">
+      <c r="G6" s="367">
         <f>K6/$E$5</f>
         <v>0.78125008888888881</v>
       </c>
-      <c r="H6" s="364"/>
+      <c r="H6" s="367"/>
       <c r="I6" s="183" t="s">
         <v>479</v>
       </c>
@@ -9353,11 +9676,11 @@
         <v>351562.54</v>
       </c>
       <c r="L6" s="165"/>
-      <c r="M6" s="364">
+      <c r="M6" s="367">
         <f>Q6/$E$5</f>
         <v>0.21874991111111111</v>
       </c>
-      <c r="N6" s="364"/>
+      <c r="N6" s="367"/>
       <c r="O6" s="186" t="s">
         <v>480</v>
       </c>
@@ -12420,23 +12743,23 @@
     </row>
     <row r="65" spans="1:19" ht="11.25" customHeight="1">
       <c r="A65" s="159"/>
-      <c r="C65" s="365" t="s">
+      <c r="C65" s="368" t="s">
         <v>506</v>
       </c>
-      <c r="D65" s="365"/>
-      <c r="E65" s="365"/>
-      <c r="G65" s="366">
+      <c r="D65" s="368"/>
+      <c r="E65" s="368"/>
+      <c r="G65" s="369">
         <f>G64</f>
         <v>0.76489628736228321</v>
       </c>
-      <c r="H65" s="366"/>
+      <c r="H65" s="369"/>
       <c r="I65" s="151"/>
       <c r="J65" s="147"/>
-      <c r="M65" s="366">
+      <c r="M65" s="369">
         <f>M64</f>
         <v>0.23510371263771726</v>
       </c>
-      <c r="N65" s="366"/>
+      <c r="N65" s="369"/>
       <c r="P65" s="147"/>
       <c r="Q65" s="149"/>
       <c r="R65" s="147"/>
@@ -12444,15 +12767,15 @@
     </row>
     <row r="66" spans="1:19" ht="11.25" customHeight="1">
       <c r="A66" s="159"/>
-      <c r="C66" s="365"/>
-      <c r="D66" s="365"/>
-      <c r="E66" s="365"/>
-      <c r="G66" s="366"/>
-      <c r="H66" s="366"/>
+      <c r="C66" s="368"/>
+      <c r="D66" s="368"/>
+      <c r="E66" s="368"/>
+      <c r="G66" s="369"/>
+      <c r="H66" s="369"/>
       <c r="I66" s="151"/>
       <c r="J66" s="147"/>
-      <c r="M66" s="366"/>
-      <c r="N66" s="366"/>
+      <c r="M66" s="369"/>
+      <c r="N66" s="369"/>
       <c r="P66" s="147"/>
       <c r="Q66" s="149"/>
       <c r="R66" s="147"/>
@@ -12879,12 +13202,6 @@
     <row r="1048548" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="G2:K2"/>
-    <mergeCell ref="M2:Q2"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="M3:O3"/>
-    <mergeCell ref="P3:Q3"/>
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="M5:N5"/>
     <mergeCell ref="G6:H6"/>
@@ -12892,6 +13209,12 @@
     <mergeCell ref="C65:E66"/>
     <mergeCell ref="G65:H66"/>
     <mergeCell ref="M65:N66"/>
+    <mergeCell ref="G2:K2"/>
+    <mergeCell ref="M2:Q2"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="M3:O3"/>
+    <mergeCell ref="P3:Q3"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" pageOrder="overThenDown" orientation="landscape" verticalDpi="0" r:id="rId1"/>
@@ -12902,7 +13225,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:K14"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
@@ -13116,7 +13439,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:AMJ1048554"/>
   <sheetFormatPr defaultRowHeight="11.25" customHeight="1"/>
@@ -13159,7 +13482,7 @@
       <c r="G1" s="147"/>
       <c r="O1" s="150"/>
       <c r="T1" s="147"/>
-      <c r="V1" s="380" t="s">
+      <c r="V1" s="375" t="s">
         <v>514</v>
       </c>
       <c r="W1" s="253" t="s">
@@ -13188,24 +13511,24 @@
       <c r="E2" s="258"/>
       <c r="F2" s="259"/>
       <c r="G2" s="257"/>
-      <c r="H2" s="386" t="s">
+      <c r="H2" s="374" t="s">
         <v>468</v>
       </c>
-      <c r="I2" s="386"/>
-      <c r="J2" s="386"/>
-      <c r="K2" s="386"/>
-      <c r="L2" s="386"/>
+      <c r="I2" s="374"/>
+      <c r="J2" s="374"/>
+      <c r="K2" s="374"/>
+      <c r="L2" s="374"/>
       <c r="M2" s="257"/>
-      <c r="N2" s="386" t="s">
+      <c r="N2" s="374" t="s">
         <v>469</v>
       </c>
-      <c r="O2" s="386"/>
-      <c r="P2" s="386"/>
-      <c r="Q2" s="386"/>
-      <c r="R2" s="386"/>
+      <c r="O2" s="374"/>
+      <c r="P2" s="374"/>
+      <c r="Q2" s="374"/>
+      <c r="R2" s="374"/>
       <c r="S2" s="257"/>
       <c r="T2" s="260"/>
-      <c r="V2" s="380"/>
+      <c r="V2" s="375"/>
       <c r="W2" s="261" t="s">
         <v>274</v>
       </c>
@@ -13353,11 +13676,11 @@
       </c>
       <c r="F5" s="276"/>
       <c r="G5" s="165"/>
-      <c r="H5" s="385">
+      <c r="H5" s="371">
         <f>L5/$E$4</f>
         <v>0.78125008888888881</v>
       </c>
-      <c r="I5" s="385"/>
+      <c r="I5" s="371"/>
       <c r="J5" s="183" t="s">
         <v>520</v>
       </c>
@@ -13369,11 +13692,11 @@
         <v>351562.54</v>
       </c>
       <c r="M5" s="165"/>
-      <c r="N5" s="385">
+      <c r="N5" s="371">
         <f>R5/$E$4</f>
         <v>0.21874991111111111</v>
       </c>
-      <c r="O5" s="385"/>
+      <c r="O5" s="371"/>
       <c r="P5" s="186" t="s">
         <v>480</v>
       </c>
@@ -13511,49 +13834,49 @@
       </c>
       <c r="F8" s="280"/>
       <c r="G8" s="157"/>
-      <c r="H8" s="377" t="s">
+      <c r="H8" s="372" t="s">
         <v>472</v>
       </c>
-      <c r="I8" s="377"/>
+      <c r="I8" s="372"/>
       <c r="J8" s="157"/>
-      <c r="K8" s="378" t="s">
+      <c r="K8" s="373" t="s">
         <v>473</v>
       </c>
-      <c r="L8" s="378"/>
+      <c r="L8" s="373"/>
       <c r="M8" s="157"/>
-      <c r="N8" s="377" t="s">
+      <c r="N8" s="372" t="s">
         <v>472</v>
       </c>
-      <c r="O8" s="377"/>
-      <c r="P8" s="377"/>
-      <c r="Q8" s="378" t="s">
+      <c r="O8" s="372"/>
+      <c r="P8" s="372"/>
+      <c r="Q8" s="373" t="s">
         <v>473</v>
       </c>
-      <c r="R8" s="378"/>
+      <c r="R8" s="373"/>
       <c r="S8" s="157"/>
       <c r="T8" s="275" t="s">
         <v>353</v>
       </c>
-      <c r="V8" s="383" t="s">
+      <c r="V8" s="381" t="s">
         <v>522</v>
       </c>
-      <c r="W8" s="384">
+      <c r="W8" s="382">
         <f>SUM(W3:W7)</f>
         <v>626102.71</v>
       </c>
-      <c r="X8" s="375">
+      <c r="X8" s="379">
         <f>SUM(X3:X7)</f>
         <v>626102.71</v>
       </c>
-      <c r="Y8" s="376">
+      <c r="Y8" s="380">
         <f>SUM(Y3:Y7)</f>
         <v>52881.886530994983</v>
       </c>
-      <c r="Z8" s="375">
+      <c r="Z8" s="379">
         <f>SUM(Z3:Z7)</f>
         <v>-152695.79399999999</v>
       </c>
-      <c r="AA8" s="376">
+      <c r="AA8" s="380">
         <f>SUM(AA3:AA7)</f>
         <v>-20182.568581486634</v>
       </c>
@@ -13613,16 +13936,16 @@
       <c r="T9" s="286" t="s">
         <v>475</v>
       </c>
-      <c r="V9" s="383"/>
-      <c r="W9" s="384"/>
-      <c r="X9" s="375"/>
-      <c r="Y9" s="376"/>
-      <c r="Z9" s="375"/>
-      <c r="AA9" s="376"/>
-      <c r="AB9" s="379" t="s">
+      <c r="V9" s="381"/>
+      <c r="W9" s="382"/>
+      <c r="X9" s="379"/>
+      <c r="Y9" s="380"/>
+      <c r="Z9" s="379"/>
+      <c r="AA9" s="380"/>
+      <c r="AB9" s="376" t="s">
         <v>524</v>
       </c>
-      <c r="AC9" s="379"/>
+      <c r="AC9" s="376"/>
     </row>
     <row r="10" spans="1:30" ht="11.25" customHeight="1" thickBot="1">
       <c r="A10" s="190">
@@ -13710,10 +14033,10 @@
       <c r="T11" s="268">
         <v>5.52</v>
       </c>
-      <c r="V11" s="380" t="s">
+      <c r="V11" s="375" t="s">
         <v>525</v>
       </c>
-      <c r="W11" s="381">
+      <c r="W11" s="377">
         <f>H83</f>
         <v>0.76489628736228321</v>
       </c>
@@ -13789,8 +14112,8 @@
       <c r="T12" s="268">
         <v>5.52</v>
       </c>
-      <c r="V12" s="380"/>
-      <c r="W12" s="381"/>
+      <c r="V12" s="375"/>
+      <c r="W12" s="377"/>
       <c r="X12" s="262" t="s">
         <v>274</v>
       </c>
@@ -13832,7 +14155,7 @@
       <c r="V13" s="268">
         <v>2018</v>
       </c>
-      <c r="W13" s="381"/>
+      <c r="W13" s="377"/>
       <c r="X13" s="270">
         <f>I15</f>
         <v>16406.251866666666</v>
@@ -13883,7 +14206,7 @@
       <c r="V14" s="268">
         <v>2019</v>
       </c>
-      <c r="W14" s="381"/>
+      <c r="W14" s="377"/>
       <c r="X14" s="270">
         <f>I25</f>
         <v>20699.204717171131</v>
@@ -13948,7 +14271,7 @@
       <c r="V15" s="268">
         <v>2020</v>
       </c>
-      <c r="W15" s="381"/>
+      <c r="W15" s="377"/>
       <c r="X15" s="270">
         <f>I42</f>
         <v>50197.878908060913</v>
@@ -14011,7 +14334,7 @@
       <c r="V16" s="268">
         <v>2021</v>
       </c>
-      <c r="W16" s="381"/>
+      <c r="W16" s="377"/>
       <c r="X16" s="270">
         <f>I60</f>
         <v>118343.48939231082</v>
@@ -14081,7 +14404,7 @@
       <c r="V17" s="268">
         <v>2022</v>
       </c>
-      <c r="W17" s="381"/>
+      <c r="W17" s="377"/>
       <c r="X17" s="270">
         <f>I86</f>
         <v>278815.57683497586</v>
@@ -14122,23 +14445,23 @@
       <c r="P18" s="151"/>
       <c r="R18" s="197"/>
       <c r="T18" s="268"/>
-      <c r="V18" s="382" t="s">
+      <c r="V18" s="378" t="s">
         <v>522</v>
       </c>
-      <c r="W18" s="381"/>
-      <c r="X18" s="375">
+      <c r="W18" s="377"/>
+      <c r="X18" s="379">
         <f>SUM(X13:X17)</f>
         <v>484462.40171918541</v>
       </c>
-      <c r="Y18" s="376">
+      <c r="Y18" s="380">
         <f>SUM(Y13:Y17)</f>
         <v>41014.400897168583</v>
       </c>
-      <c r="Z18" s="375">
+      <c r="Z18" s="379">
         <f>SUM(Z13:Z17)</f>
         <v>-118496.37278704304</v>
       </c>
-      <c r="AA18" s="376">
+      <c r="AA18" s="380">
         <f>SUM(AA13:AA17)</f>
         <v>-15674.29363463297</v>
       </c>
@@ -14174,16 +14497,16 @@
       <c r="R19" s="158"/>
       <c r="S19" s="156"/>
       <c r="T19" s="290"/>
-      <c r="V19" s="382"/>
-      <c r="W19" s="381"/>
-      <c r="X19" s="375"/>
-      <c r="Y19" s="376"/>
-      <c r="Z19" s="375"/>
-      <c r="AA19" s="376"/>
-      <c r="AB19" s="379" t="s">
+      <c r="V19" s="378"/>
+      <c r="W19" s="377"/>
+      <c r="X19" s="379"/>
+      <c r="Y19" s="380"/>
+      <c r="Z19" s="379"/>
+      <c r="AA19" s="380"/>
+      <c r="AB19" s="376" t="s">
         <v>530</v>
       </c>
-      <c r="AC19" s="379"/>
+      <c r="AC19" s="376"/>
     </row>
     <row r="20" spans="1:29" s="145" customFormat="1" ht="11.25" customHeight="1" thickBot="1">
       <c r="A20" s="159" t="s">
@@ -14310,10 +14633,10 @@
       <c r="T21" s="268">
         <v>5.73</v>
       </c>
-      <c r="V21" s="380" t="s">
+      <c r="V21" s="375" t="s">
         <v>531</v>
       </c>
-      <c r="W21" s="381">
+      <c r="W21" s="377">
         <f>N83</f>
         <v>0.23510371263771726</v>
       </c>
@@ -14389,8 +14712,8 @@
       <c r="T22" s="268">
         <v>5.73</v>
       </c>
-      <c r="V22" s="380"/>
-      <c r="W22" s="381"/>
+      <c r="V22" s="375"/>
+      <c r="W22" s="377"/>
       <c r="X22" s="262" t="s">
         <v>274</v>
       </c>
@@ -14422,7 +14745,7 @@
       <c r="V23" s="268">
         <v>2018</v>
       </c>
-      <c r="W23" s="381"/>
+      <c r="W23" s="377"/>
       <c r="X23" s="270">
         <f>O15</f>
         <v>4593.7481333333335</v>
@@ -14474,7 +14797,7 @@
       <c r="V24" s="268">
         <v>2019</v>
       </c>
-      <c r="W24" s="381"/>
+      <c r="W24" s="377"/>
       <c r="X24" s="270">
         <f>O25</f>
         <v>5800.7952828288689</v>
@@ -14538,7 +14861,7 @@
       <c r="V25" s="268">
         <v>2020</v>
       </c>
-      <c r="W25" s="381"/>
+      <c r="W25" s="377"/>
       <c r="X25" s="270">
         <f>O42</f>
         <v>14302.121091939091</v>
@@ -14601,7 +14924,7 @@
       <c r="V26" s="268">
         <v>2021</v>
       </c>
-      <c r="W26" s="381"/>
+      <c r="W26" s="377"/>
       <c r="X26" s="270">
         <f>O60</f>
         <v>33916.510607689197</v>
@@ -14671,7 +14994,7 @@
       <c r="V27" s="268">
         <v>2022</v>
       </c>
-      <c r="W27" s="381"/>
+      <c r="W27" s="377"/>
       <c r="X27" s="270">
         <f>O86</f>
         <v>83027.133165024279</v>
@@ -14708,23 +15031,23 @@
       <c r="P28" s="151"/>
       <c r="R28" s="197"/>
       <c r="T28" s="268"/>
-      <c r="V28" s="382" t="s">
+      <c r="V28" s="378" t="s">
         <v>522</v>
       </c>
-      <c r="W28" s="381"/>
-      <c r="X28" s="375">
+      <c r="W28" s="377"/>
+      <c r="X28" s="379">
         <f>SUM(X23:X27)</f>
         <v>141640.30828081479</v>
       </c>
-      <c r="Y28" s="376">
+      <c r="Y28" s="380">
         <f>SUM(Y23:Y27)</f>
         <v>11867.485633826394</v>
       </c>
-      <c r="Z28" s="375">
+      <c r="Z28" s="379">
         <f>SUM(Z23:Z27)</f>
         <v>-34199.421212956979</v>
       </c>
-      <c r="AA28" s="376">
+      <c r="AA28" s="380">
         <f>SUM(AA23:AA27)</f>
         <v>-4508.2749468536649</v>
       </c>
@@ -14760,16 +15083,16 @@
       <c r="R29" s="158"/>
       <c r="S29" s="156"/>
       <c r="T29" s="290"/>
-      <c r="V29" s="382"/>
-      <c r="W29" s="381"/>
-      <c r="X29" s="375"/>
-      <c r="Y29" s="376"/>
-      <c r="Z29" s="375"/>
-      <c r="AA29" s="376"/>
-      <c r="AB29" s="379" t="s">
+      <c r="V29" s="378"/>
+      <c r="W29" s="377"/>
+      <c r="X29" s="379"/>
+      <c r="Y29" s="380"/>
+      <c r="Z29" s="379"/>
+      <c r="AA29" s="380"/>
+      <c r="AB29" s="376" t="s">
         <v>536</v>
       </c>
-      <c r="AC29" s="379"/>
+      <c r="AC29" s="376"/>
     </row>
     <row r="30" spans="1:29" s="145" customFormat="1" ht="11.25" customHeight="1" thickBot="1">
       <c r="A30" s="159" t="s">
@@ -14902,14 +15225,14 @@
         <v>510</v>
       </c>
       <c r="Y31" s="370"/>
-      <c r="Z31" s="371" t="s">
+      <c r="Z31" s="383" t="s">
         <v>28</v>
       </c>
-      <c r="AA31" s="371"/>
-      <c r="AB31" s="372" t="s">
+      <c r="AA31" s="383"/>
+      <c r="AB31" s="384" t="s">
         <v>516</v>
       </c>
-      <c r="AC31" s="372"/>
+      <c r="AC31" s="384"/>
     </row>
     <row r="32" spans="1:29" s="145" customFormat="1" ht="11.25" customHeight="1" thickBot="1">
       <c r="A32" s="159" t="s">
@@ -15053,23 +15376,23 @@
       <c r="T33" s="268">
         <v>7.93</v>
       </c>
-      <c r="V33" s="374" t="s">
+      <c r="V33" s="386" t="s">
         <v>537</v>
       </c>
-      <c r="W33" s="374"/>
-      <c r="X33" s="375">
+      <c r="W33" s="386"/>
+      <c r="X33" s="379">
         <f>X28+X18</f>
         <v>626102.7100000002</v>
       </c>
-      <c r="Y33" s="376">
+      <c r="Y33" s="380">
         <f>Y28+Y18</f>
         <v>52881.886530994976</v>
       </c>
-      <c r="Z33" s="375">
+      <c r="Z33" s="379">
         <f>Z28+Z18</f>
         <v>-152695.79400000002</v>
       </c>
-      <c r="AA33" s="376">
+      <c r="AA33" s="380">
         <f>AA28+AA18</f>
         <v>-20182.568581486634</v>
       </c>
@@ -15141,16 +15464,16 @@
       <c r="T34" s="268">
         <v>7.93</v>
       </c>
-      <c r="V34" s="374"/>
-      <c r="W34" s="374"/>
-      <c r="X34" s="375"/>
-      <c r="Y34" s="376"/>
-      <c r="Z34" s="375"/>
-      <c r="AA34" s="376"/>
-      <c r="AB34" s="379" t="s">
+      <c r="V34" s="386"/>
+      <c r="W34" s="386"/>
+      <c r="X34" s="379"/>
+      <c r="Y34" s="380"/>
+      <c r="Z34" s="379"/>
+      <c r="AA34" s="380"/>
+      <c r="AB34" s="376" t="s">
         <v>524</v>
       </c>
-      <c r="AC34" s="379"/>
+      <c r="AC34" s="376"/>
     </row>
     <row r="35" spans="1:29" s="145" customFormat="1" ht="11.25" customHeight="1">
       <c r="A35" s="159" t="s">
@@ -15334,16 +15657,16 @@
       <c r="T37" s="268">
         <v>8.7899999999999991</v>
       </c>
-      <c r="V37" s="374" t="s">
+      <c r="V37" s="386" t="s">
         <v>538</v>
       </c>
-      <c r="W37" s="374"/>
-      <c r="X37" s="374"/>
-      <c r="Y37" s="374"/>
-      <c r="Z37" s="374"/>
-      <c r="AA37" s="374"/>
-      <c r="AB37" s="374"/>
-      <c r="AC37" s="374"/>
+      <c r="W37" s="386"/>
+      <c r="X37" s="386"/>
+      <c r="Y37" s="386"/>
+      <c r="Z37" s="386"/>
+      <c r="AA37" s="386"/>
+      <c r="AB37" s="386"/>
+      <c r="AC37" s="386"/>
     </row>
     <row r="38" spans="1:29" s="145" customFormat="1" ht="11.25" customHeight="1">
       <c r="A38" s="159" t="s">
@@ -15747,25 +16070,25 @@
       </c>
       <c r="F45" s="280"/>
       <c r="G45" s="157"/>
-      <c r="H45" s="377" t="s">
+      <c r="H45" s="372" t="s">
         <v>472</v>
       </c>
-      <c r="I45" s="377"/>
+      <c r="I45" s="372"/>
       <c r="J45" s="157"/>
-      <c r="K45" s="378" t="s">
+      <c r="K45" s="373" t="s">
         <v>473</v>
       </c>
-      <c r="L45" s="378"/>
+      <c r="L45" s="373"/>
       <c r="M45" s="157"/>
-      <c r="N45" s="377" t="s">
+      <c r="N45" s="372" t="s">
         <v>472</v>
       </c>
-      <c r="O45" s="377"/>
-      <c r="P45" s="377"/>
-      <c r="Q45" s="378" t="s">
+      <c r="O45" s="372"/>
+      <c r="P45" s="372"/>
+      <c r="Q45" s="373" t="s">
         <v>473</v>
       </c>
-      <c r="R45" s="378"/>
+      <c r="R45" s="373"/>
       <c r="S45" s="157"/>
       <c r="T45" s="275" t="s">
         <v>353</v>
@@ -19862,22 +20185,22 @@
         <v>558</v>
       </c>
       <c r="G84" s="334"/>
-      <c r="H84" s="373">
+      <c r="H84" s="385">
         <f>H83</f>
         <v>0.76489628736228321</v>
       </c>
-      <c r="I84" s="373"/>
+      <c r="I84" s="385"/>
       <c r="J84" s="335" t="s">
         <v>468</v>
       </c>
       <c r="K84" s="334"/>
       <c r="L84" s="336"/>
       <c r="M84" s="332"/>
-      <c r="N84" s="373">
+      <c r="N84" s="385">
         <f>N83</f>
         <v>0.23510371263771726</v>
       </c>
-      <c r="O84" s="373"/>
+      <c r="O84" s="385"/>
       <c r="P84" s="337" t="s">
         <v>469</v>
       </c>
@@ -48784,18 +49107,35 @@
     </row>
   </sheetData>
   <mergeCells count="57">
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="AB1:AC1"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="N2:R2"/>
-    <mergeCell ref="Q8:R8"/>
-    <mergeCell ref="V1:V2"/>
-    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="X31:Y31"/>
+    <mergeCell ref="Z31:AA31"/>
+    <mergeCell ref="AB31:AC31"/>
+    <mergeCell ref="H84:I84"/>
+    <mergeCell ref="N84:O84"/>
+    <mergeCell ref="V33:W34"/>
+    <mergeCell ref="X33:X34"/>
+    <mergeCell ref="Y33:Y34"/>
+    <mergeCell ref="V37:AC37"/>
+    <mergeCell ref="H45:I45"/>
+    <mergeCell ref="K45:L45"/>
+    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="Q45:R45"/>
+    <mergeCell ref="Z33:Z34"/>
+    <mergeCell ref="AA33:AA34"/>
+    <mergeCell ref="AB34:AC34"/>
+    <mergeCell ref="AA18:AA19"/>
+    <mergeCell ref="AB19:AC19"/>
+    <mergeCell ref="V21:V22"/>
+    <mergeCell ref="W21:W29"/>
+    <mergeCell ref="X21:Y21"/>
+    <mergeCell ref="Z21:AA21"/>
+    <mergeCell ref="AB21:AC21"/>
+    <mergeCell ref="V28:V29"/>
+    <mergeCell ref="X28:X29"/>
+    <mergeCell ref="Y28:Y29"/>
+    <mergeCell ref="Z28:Z29"/>
+    <mergeCell ref="AA28:AA29"/>
+    <mergeCell ref="AB29:AC29"/>
     <mergeCell ref="AB9:AC9"/>
     <mergeCell ref="V11:V12"/>
     <mergeCell ref="W11:W19"/>
@@ -48812,35 +49152,18 @@
     <mergeCell ref="Y8:Y9"/>
     <mergeCell ref="Z8:Z9"/>
     <mergeCell ref="AA8:AA9"/>
-    <mergeCell ref="AA18:AA19"/>
-    <mergeCell ref="AB19:AC19"/>
-    <mergeCell ref="V21:V22"/>
-    <mergeCell ref="W21:W29"/>
-    <mergeCell ref="X21:Y21"/>
-    <mergeCell ref="Z21:AA21"/>
-    <mergeCell ref="AB21:AC21"/>
-    <mergeCell ref="V28:V29"/>
-    <mergeCell ref="X28:X29"/>
-    <mergeCell ref="Y28:Y29"/>
-    <mergeCell ref="Z28:Z29"/>
-    <mergeCell ref="AA28:AA29"/>
-    <mergeCell ref="AB29:AC29"/>
-    <mergeCell ref="X31:Y31"/>
-    <mergeCell ref="Z31:AA31"/>
-    <mergeCell ref="AB31:AC31"/>
-    <mergeCell ref="H84:I84"/>
-    <mergeCell ref="N84:O84"/>
-    <mergeCell ref="V33:W34"/>
-    <mergeCell ref="X33:X34"/>
-    <mergeCell ref="Y33:Y34"/>
-    <mergeCell ref="V37:AC37"/>
-    <mergeCell ref="H45:I45"/>
-    <mergeCell ref="K45:L45"/>
-    <mergeCell ref="N45:P45"/>
-    <mergeCell ref="Q45:R45"/>
-    <mergeCell ref="Z33:Z34"/>
-    <mergeCell ref="AA33:AA34"/>
-    <mergeCell ref="AB34:AC34"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="AB1:AC1"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="N2:R2"/>
+    <mergeCell ref="Q8:R8"/>
+    <mergeCell ref="V1:V2"/>
+    <mergeCell ref="X1:Y1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.30000000000000004" footer="0.30000000000000004"/>
   <pageSetup paperSize="0" fitToWidth="0" fitToHeight="0" pageOrder="overThenDown" orientation="landscape" horizontalDpi="0" verticalDpi="0" copies="0"/>
@@ -48852,6 +49175,246 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A6:F22"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="12.140625" customWidth="1"/>
+    <col min="2" max="2" width="26.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="C7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="3">
+        <f>'SnyA105-22'!E4</f>
+        <v>84000</v>
+      </c>
+      <c r="D8" s="3">
+        <f>'SnyA105-22'!F4</f>
+        <v>84000</v>
+      </c>
+      <c r="E8" s="4">
+        <f t="shared" ref="E8:E13" si="0">C8-D8</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="4">
+        <f>'SnyA105-22'!E6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="3">
+        <f>'SnyB202-22'!D4</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="3">
+        <f>'SnyB202-22'!E4</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F9" s="4">
+        <f>'SnyB202-22'!D6</f>
+        <v>-1000.1199999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="3">
+        <f>'SnyC301-22'!D4</f>
+        <v>240000</v>
+      </c>
+      <c r="D10" s="3">
+        <f>'SnyC301-22'!E4</f>
+        <v>135000</v>
+      </c>
+      <c r="E10" s="4">
+        <f t="shared" si="0"/>
+        <v>105000</v>
+      </c>
+      <c r="F10" s="4">
+        <f>'SnyC301-22'!D6</f>
+        <v>-3924.1099999999997</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="3">
+        <f>'SnyE502-22'!D4</f>
+        <v>96000</v>
+      </c>
+      <c r="D11" s="3">
+        <f>'SnyE502-22'!E4</f>
+        <v>89000</v>
+      </c>
+      <c r="E11" s="4">
+        <f t="shared" si="0"/>
+        <v>7000</v>
+      </c>
+      <c r="F11" s="4">
+        <f>'SnyE502-22'!D6</f>
+        <v>-800</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="3">
+        <f>'SnyF601-22'!D4</f>
+        <v>109312.51909485454</v>
+      </c>
+      <c r="D12" s="3">
+        <f>'SnyF601-22'!E4</f>
+        <v>109312.51999999999</v>
+      </c>
+      <c r="E12" s="4">
+        <f t="shared" si="0"/>
+        <v>-9.0514545445330441E-4</v>
+      </c>
+      <c r="F12" s="4">
+        <f>'SnyF601-22'!D6</f>
+        <v>-2510.63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="3">
+        <f>'SnyG702-22'!D4</f>
+        <v>96000</v>
+      </c>
+      <c r="D13" s="3">
+        <f>'SnyG702-22'!E4</f>
+        <v>96000</v>
+      </c>
+      <c r="E13" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F13" s="4">
+        <f>'SnyG702-22'!D6</f>
+        <v>-1200</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="4">
+        <f>SnH_yazıhane!F2*-1</f>
+        <v>-5725.95</v>
+      </c>
+      <c r="D14" s="4">
+        <f>C14</f>
+        <v>-5725.95</v>
+      </c>
+      <c r="E14" s="4">
+        <f>C14-D14</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="E15" s="4"/>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="B16" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="6">
+        <f>SUM(C8:C14)</f>
+        <v>619586.56909485464</v>
+      </c>
+      <c r="D16" s="6">
+        <f>SUM(D8:D14)</f>
+        <v>507586.57</v>
+      </c>
+      <c r="E16" s="6">
+        <f>SUM(E8:E14)</f>
+        <v>111999.99909485455</v>
+      </c>
+      <c r="F16" s="6">
+        <f>SUM(F8:F14)</f>
+        <v>-9434.86</v>
+      </c>
+    </row>
+    <row r="18" spans="4:4">
+      <c r="D18" s="359"/>
+    </row>
+    <row r="22" spans="4:4">
+      <c r="D22" s="361"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.39370078740157505" right="0.23622047244094502" top="0.70905511811023614" bottom="0.7062992125984251" header="0.31535433070866109" footer="0.3125984251968501"/>
+  <pageSetup paperSize="0" fitToWidth="0" fitToHeight="0" pageOrder="overThenDown" orientation="landscape" horizontalDpi="0" verticalDpi="0" copies="0"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H104"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
@@ -49980,7 +50543,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H86"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
@@ -50885,7 +51448,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G99"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
@@ -52054,7 +52617,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:H84"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
@@ -53037,7 +53600,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:L109"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
@@ -54514,7 +55077,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AFC9CE6-0D54-443A-AAB2-0B9FD02F7EE3}">
   <dimension ref="B4:I24"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
@@ -54857,7 +55420,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:G71"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
@@ -55747,426 +56310,4 @@
   <pageSetup paperSize="0" fitToWidth="0" fitToHeight="0" pageOrder="overThenDown" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:G48"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
-  <cols>
-    <col min="1" max="1" width="10.7109375" customWidth="1"/>
-    <col min="2" max="2" width="23.7109375" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" style="3" customWidth="1"/>
-    <col min="4" max="4" width="10.5703125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="9.42578125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="10.5703125" style="3" customWidth="1"/>
-    <col min="7" max="7" width="11.28515625" style="3" customWidth="1"/>
-    <col min="8" max="59" width="12.140625" customWidth="1"/>
-    <col min="60" max="60" width="9.140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7">
-      <c r="B1" s="1"/>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>2023</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>601</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="F2" s="57">
-        <f>SUM(F6:F56)</f>
-        <v>5725.95</v>
-      </c>
-      <c r="G2" s="57">
-        <f>F2</f>
-        <v>5725.95</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="99" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="99" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="100" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="100" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="100" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="100" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" s="100" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="F5" s="97"/>
-      <c r="G5" s="57"/>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="60">
-        <v>44956</v>
-      </c>
-      <c r="B6" t="s">
-        <v>255</v>
-      </c>
-      <c r="C6"/>
-      <c r="D6"/>
-      <c r="F6" s="3">
-        <v>87.69</v>
-      </c>
-      <c r="G6" s="3">
-        <f t="shared" ref="G6:G23" si="0">G5+E6-F6</f>
-        <v>-87.69</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="60">
-        <v>44985</v>
-      </c>
-      <c r="B7" t="s">
-        <v>256</v>
-      </c>
-      <c r="C7"/>
-      <c r="D7"/>
-      <c r="F7" s="3">
-        <v>54.93</v>
-      </c>
-      <c r="G7" s="3">
-        <f t="shared" si="0"/>
-        <v>-142.62</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="60">
-        <v>45015</v>
-      </c>
-      <c r="B8" t="s">
-        <v>257</v>
-      </c>
-      <c r="C8"/>
-      <c r="D8"/>
-      <c r="F8" s="3">
-        <v>97.14</v>
-      </c>
-      <c r="G8" s="3">
-        <f t="shared" si="0"/>
-        <v>-239.76</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="60">
-        <v>45046</v>
-      </c>
-      <c r="B9" t="s">
-        <v>258</v>
-      </c>
-      <c r="C9"/>
-      <c r="D9"/>
-      <c r="F9" s="3">
-        <v>99.31</v>
-      </c>
-      <c r="G9" s="3">
-        <f t="shared" si="0"/>
-        <v>-339.07</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="60">
-        <v>45076</v>
-      </c>
-      <c r="B10" t="s">
-        <v>259</v>
-      </c>
-      <c r="C10"/>
-      <c r="D10"/>
-      <c r="F10" s="3">
-        <v>34.06</v>
-      </c>
-      <c r="G10" s="3">
-        <f t="shared" si="0"/>
-        <v>-373.13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="101">
-        <v>45060</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="C11"/>
-      <c r="D11"/>
-      <c r="F11" s="3">
-        <v>1095</v>
-      </c>
-      <c r="G11" s="3">
-        <f t="shared" si="0"/>
-        <v>-1468.13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="101">
-        <v>45060</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="C12"/>
-      <c r="D12"/>
-      <c r="F12" s="3">
-        <v>109.5</v>
-      </c>
-      <c r="G12" s="3">
-        <f t="shared" si="0"/>
-        <v>-1577.63</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="60">
-        <v>45107</v>
-      </c>
-      <c r="B13" t="s">
-        <v>262</v>
-      </c>
-      <c r="C13"/>
-      <c r="D13"/>
-      <c r="F13" s="3">
-        <v>22.7</v>
-      </c>
-      <c r="G13" s="3">
-        <f t="shared" si="0"/>
-        <v>-1600.3300000000002</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="60">
-        <v>45137</v>
-      </c>
-      <c r="B14" t="s">
-        <v>263</v>
-      </c>
-      <c r="C14"/>
-      <c r="D14"/>
-      <c r="F14" s="3">
-        <v>31.73</v>
-      </c>
-      <c r="G14" s="3">
-        <f t="shared" si="0"/>
-        <v>-1632.0600000000002</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="60">
-        <v>45168</v>
-      </c>
-      <c r="B15" t="s">
-        <v>264</v>
-      </c>
-      <c r="C15"/>
-      <c r="D15"/>
-      <c r="F15" s="3">
-        <v>34.99</v>
-      </c>
-      <c r="G15" s="3">
-        <f t="shared" si="0"/>
-        <v>-1667.0500000000002</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="60">
-        <v>45199</v>
-      </c>
-      <c r="B16" t="s">
-        <v>265</v>
-      </c>
-      <c r="C16"/>
-      <c r="D16"/>
-      <c r="F16" s="3">
-        <v>23.73</v>
-      </c>
-      <c r="G16" s="3">
-        <f t="shared" si="0"/>
-        <v>-1690.7800000000002</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="60">
-        <v>45229</v>
-      </c>
-      <c r="B17" t="s">
-        <v>266</v>
-      </c>
-      <c r="C17"/>
-      <c r="D17"/>
-      <c r="F17" s="3">
-        <v>41.12</v>
-      </c>
-      <c r="G17" s="3">
-        <f t="shared" si="0"/>
-        <v>-1731.9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="101">
-        <v>45213</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="C18"/>
-      <c r="D18"/>
-      <c r="F18" s="3">
-        <v>1095</v>
-      </c>
-      <c r="G18" s="3">
-        <f t="shared" si="0"/>
-        <v>-2826.9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="101">
-        <v>45213</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="C19"/>
-      <c r="D19"/>
-      <c r="F19" s="3">
-        <v>109.5</v>
-      </c>
-      <c r="G19" s="3">
-        <f t="shared" si="0"/>
-        <v>-2936.4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="361">
-        <v>45257</v>
-      </c>
-      <c r="B20" t="s">
-        <v>600</v>
-      </c>
-      <c r="F20" s="3">
-        <v>2500</v>
-      </c>
-      <c r="G20" s="3">
-        <f t="shared" si="0"/>
-        <v>-5436.4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="60">
-        <v>45260</v>
-      </c>
-      <c r="B21" t="s">
-        <v>267</v>
-      </c>
-      <c r="C21"/>
-      <c r="D21"/>
-      <c r="F21" s="3">
-        <v>41.54</v>
-      </c>
-      <c r="G21" s="3">
-        <f t="shared" si="0"/>
-        <v>-5477.94</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="60">
-        <v>45290</v>
-      </c>
-      <c r="B22" t="s">
-        <v>270</v>
-      </c>
-      <c r="C22"/>
-      <c r="F22" s="3">
-        <v>128.01</v>
-      </c>
-      <c r="G22" s="3">
-        <f t="shared" si="0"/>
-        <v>-5605.95</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="B23" t="s">
-        <v>144</v>
-      </c>
-      <c r="C23"/>
-      <c r="D23"/>
-      <c r="E23"/>
-      <c r="F23">
-        <v>120</v>
-      </c>
-      <c r="G23" s="3">
-        <f t="shared" si="0"/>
-        <v>-5725.95</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="C24"/>
-      <c r="D24"/>
-      <c r="E24"/>
-      <c r="F24"/>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="D25"/>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="60"/>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="60"/>
-      <c r="B27" s="3"/>
-      <c r="D27"/>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="60"/>
-      <c r="B28" s="3"/>
-      <c r="D28"/>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="E32" s="1"/>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="E33" s="1"/>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="E34" s="1"/>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35" s="60"/>
-      <c r="E35" s="1"/>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36" s="60"/>
-      <c r="E36" s="1"/>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="E37" s="1"/>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38" s="60"/>
-      <c r="E38" s="1"/>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="G48" s="57"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.39370078740157505" right="0.23622047244094502" top="0.70905511811023614" bottom="0.7062992125984251" header="0.31535433070866109" footer="0.3125984251968501"/>
-  <pageSetup paperSize="0" fitToWidth="0" fitToHeight="0" pageOrder="overThenDown" orientation="landscape" horizontalDpi="0" verticalDpi="0" copies="0"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
 </file>